--- a/src/assets/CifDocumentsTemplates/100005.xlsx
+++ b/src/assets/CifDocumentsTemplates/100005.xlsx
@@ -11,17 +11,168 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_GoBack" localSheetId="0">Sheet1!$B$8</definedName>
+  </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+  <si>
+    <t>Instrument Name</t>
+  </si>
+  <si>
+    <t>Internal (per sample)</t>
+  </si>
+  <si>
+    <t>Academia/R&amp;D (per sample)</t>
+  </si>
+  <si>
+    <t>Industry (per sample)</t>
+  </si>
+  <si>
+    <t>Inductively Coupled Plasma Optical Emission Spectrometry (PerkinElmer ICP-OES Optima 8000)</t>
+  </si>
+  <si>
+    <r>
+      <t>500/- per sample (upto 1 elements)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>**</t>
+    </r>
+  </si>
+  <si>
+    <t>and</t>
+  </si>
+  <si>
+    <t>+ 150/- extra for additional element</t>
+  </si>
+  <si>
+    <r>
+      <t>Note:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [1] Standards will be provided by the user only. [2] 750/- per sample will be charged extra for sample preparation (i.e., acid digestion).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>850/- per sample (upto 1 elements)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>**</t>
+    </r>
+  </si>
+  <si>
+    <t>+ 175/- extra for additional element</t>
+  </si>
+  <si>
+    <r>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1500/- per sample (upto 1 elements)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> **</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + 200/- extra for additional element</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">+ 200/- extra for additional element </t>
+  </si>
+  <si>
+    <r>
+      <t>Note:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [1] Standards will be provided by the user only. [2] 1000/- per sample will be charged extra for sample preparation (i.e., acid digestion).</t>
+    </r>
+  </si>
+  <si>
+    <t>Central instrumentation FACILITY (CIF)</t>
+  </si>
+  <si>
+    <t>Lovely Professional University</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalandhar - Delhi G.T. Road, Phagwara, Punjab (India) - 144411, </t>
+  </si>
+  <si>
+    <t>Telephone no: +911824444535, Fax no: +91824-506111, Email-id: cif@lpu.co.in</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -37,6 +188,43 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -46,7 +234,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -55,64 +243,128 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -408,187 +660,115 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J14"/>
+  <dimension ref="B2:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="11" width="21.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="70.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="11" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="5"/>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="3"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
+    <row r="2" spans="2:5" ht="15.75">
+      <c r="C2" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" ht="15.75">
+      <c r="C3" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="C4" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="C5" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="15.75" thickBot="1">
+      <c r="C6" s="11"/>
+    </row>
+    <row r="7" spans="2:5" ht="48" thickBot="1">
+      <c r="B7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="60.75">
+      <c r="B8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9" s="7"/>
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="30">
+      <c r="B10" s="7"/>
+      <c r="C10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="105">
+      <c r="B11" s="7"/>
+      <c r="C11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="15.75" thickBot="1">
+      <c r="B12" s="9"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A14:J14"/>
+  <mergeCells count="1">
+    <mergeCell ref="B8:B12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/assets/CifDocumentsTemplates/100005.xlsx
+++ b/src/assets/CifDocumentsTemplates/100005.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_GoBack" localSheetId="0">Sheet1!$B$8</definedName>
@@ -19,160 +17,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
-  <si>
-    <t>Instrument Name</t>
-  </si>
-  <si>
-    <t>Internal (per sample)</t>
-  </si>
-  <si>
-    <t>Academia/R&amp;D (per sample)</t>
-  </si>
-  <si>
-    <t>Industry (per sample)</t>
-  </si>
-  <si>
-    <t>Inductively Coupled Plasma Optical Emission Spectrometry (PerkinElmer ICP-OES Optima 8000)</t>
-  </si>
-  <si>
-    <r>
-      <t>500/- per sample (upto 1 elements)</t>
-    </r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>Information of samples for: ICP-OES</t>
+  </si>
+  <si>
+    <t>S. No.</t>
+  </si>
+  <si>
+    <t>Sample code/ID</t>
+  </si>
+  <si>
+    <t>Nature of sample (e.g., liquid, solution, etc.)</t>
+  </si>
+  <si>
+    <t>Name of elements for analysis</t>
+  </si>
+  <si>
+    <t>Wavelength range (in nm)</t>
+  </si>
+  <si>
+    <t>Any remark</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>**</t>
-    </r>
-  </si>
-  <si>
-    <t>and</t>
-  </si>
-  <si>
-    <t>+ 150/- extra for additional element</t>
-  </si>
-  <si>
-    <r>
-      <t>Note:</t>
+      <t xml:space="preserve">Note: </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> [1] Standards will be provided by the user only. [2] 750/- per sample will be charged extra for sample preparation (i.e., acid digestion).</t>
+      <t xml:space="preserve">Note: Maximum limit 5 samples per requisition form. Only, fully prepared samples should be submitted by the users. The standards should be provided along with samples by the users.  If the sample(s) are hazardous to the personnel or equipment then kindly provide appropriate handling instructions. Kindly consult CIF for sample/sample preparation before bringing your samples for analysis. Attach extra sheet for any additional information. </t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>**</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>850/- per sample (upto 1 elements)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>**</t>
-    </r>
-  </si>
-  <si>
-    <t>+ 175/- extra for additional element</t>
-  </si>
-  <si>
-    <r>
-      <t>**</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1500/- per sample (upto 1 elements)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> **</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> + 200/- extra for additional element</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">+ 200/- extra for additional element </t>
-  </si>
-  <si>
-    <r>
-      <t>Note:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> [1] Standards will be provided by the user only. [2] 1000/- per sample will be charged extra for sample preparation (i.e., acid digestion).</t>
-    </r>
-  </si>
-  <si>
-    <t>Central instrumentation FACILITY (CIF)</t>
-  </si>
-  <si>
-    <t>Lovely Professional University</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jalandhar - Delhi G.T. Road, Phagwara, Punjab (India) - 144411, </t>
-  </si>
-  <si>
-    <t>Telephone no: +911824444535, Fax no: +91824-506111, Email-id: cif@lpu.co.in</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,37 +85,7 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -234,7 +99,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -243,128 +108,112 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -660,132 +509,161 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:E12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="70.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="11" width="21.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="6" width="32.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="15.75">
-      <c r="C2" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" ht="15.75">
-      <c r="C3" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5">
-      <c r="C4" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5">
-      <c r="C5" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" ht="15.75" thickBot="1">
-      <c r="C6" s="11"/>
-    </row>
-    <row r="7" spans="2:5" ht="48" thickBot="1">
-      <c r="B7" s="1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" ht="60.75">
-      <c r="B8" s="8" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5">
-      <c r="B9" s="7"/>
-      <c r="C9" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" ht="30">
-      <c r="B10" s="7"/>
-      <c r="C10" s="3" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="22.15" customHeight="1">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="7">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="7">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="7">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="7">
+        <v>4</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="7">
+        <v>5</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="9"/>
+    </row>
+    <row r="10" spans="1:6" ht="15" customHeight="1">
+      <c r="A10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" ht="105">
-      <c r="B11" s="7"/>
-      <c r="C11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="15.75" thickBot="1">
-      <c r="B12" s="9"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="6"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B8:B12"/>
+  <mergeCells count="8">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="A10:F14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>